--- a/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
@@ -920,7 +920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Er. Aman Sethi</t>
+          <t>Prof. Aman Sethi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1070,7 +1070,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1626,7 +1626,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Er. Aman Sethi</t>
+          <t>Prof. Aman Sethi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1686,7 +1686,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1836,7 +1836,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,7 +1866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1956,7 +1956,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1986,7 +1986,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2001,7 +2001,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2016,7 +2016,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2076,7 +2076,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2106,7 +2106,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prof. Tejinder Mann</t>
+          <t>Dr. Tejinder Mann</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Er. Rajvir Garg</t>
+          <t>Prof. Rajvir Garg</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Er. Rajvir Garg</t>
+          <t>Prof. Rajvir Garg</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Er. Rajvir Garg</t>
+          <t>Prof. Rajvir Garg</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Pooja Bansal</t>
+          <t>Prof. Pooja Bansal</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Pooja Bansal</t>
+          <t>Prof. Pooja Bansal</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prof. Nitin Dhaliwal</t>
+          <t>Dr. Nitin Dhaliwal</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Er. Pooja Gill</t>
+          <t>Prof. Pooja Gill</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Er. Deepika Bains</t>
+          <t>Dr. Deepika Bains</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dr. Rohit Brar</t>
+          <t>Prof. Rohit Brar</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Prof. Shivani Chopra</t>
+          <t>Dr. Shivani Chopra</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Er. Aman Sethi</t>
+          <t>Prof. Aman Sethi</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Er. Aman Sethi</t>
+          <t>Prof. Aman Sethi</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Er. Sachin Ahluwalia</t>
+          <t>Dr. Sachin Ahluwalia</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dr. Tanvi Kohli</t>
+          <t>Prof. Tanvi Kohli</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prof. Ankush Jindal</t>
+          <t>Dr. Ankush Jindal</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Muskan Malhi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Noor Sandhu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Hargun Goyal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Sukhmani Arora</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Ishaan Thind</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Nikita Singh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Simran Bedi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Karan Sharma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Mehakpreet Grewal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Gurnoor Bhatia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Rajbir Bansal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Harleen Jain</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Navjot Gupta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Sanya Saini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Gurleen Verma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Jashan Kapoor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Fatehbir Pannu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Prabhleen Dhillon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mehakpreet Bansal</t>
+          <t>Diya Rana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gurnoor Grewal</t>
+          <t>Meher Mehta</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajbir Bedi</t>
+          <t>Sahil Aulakh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harleen Thind</t>
+          <t>Aditi Kaur</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navjot Goyal</t>
+          <t>Ekamjot Chawla</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sanya Malhi</t>
+          <t>Avneet Verma</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gurleen Gill</t>
+          <t>Manjot Kapoor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jashan Kaur</t>
+          <t>Arjun Pannu</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fatehbir Mehta</t>
+          <t>Manav Dhillon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prabhleen Dhillon</t>
+          <t>Riya Rana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diya Kapoor</t>
+          <t>Zoya Mehta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Meher Saini</t>
+          <t>Arshdeep Aulakh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sahil Jain</t>
+          <t>Yuvraj Kaur</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aditi Bhatia</t>
+          <t>Lovepreet Chawla</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ekamjot Sharma</t>
+          <t>Ananya Gill</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avneet Singh</t>
+          <t>Kavya Sidhu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manjot Arora</t>
+          <t>Rahul Malhi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arjun Sandhu</t>
+          <t>Vansh Sandhu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manav Sidhu</t>
+          <t>Sneha Goyal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riya Chawla</t>
+          <t>Taranpreet Arora</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zoya Aulakh</t>
+          <t>Khushi Thind</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arshdeep Rana</t>
+          <t>Aarav Singh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yuvraj Pannu</t>
+          <t>Kabir Bedi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lovepreet Verma</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ananya Gupta</t>
+          <t>Uday Grewal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kavya Bansal</t>
+          <t>Rohan Bhatia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rahul Grewal</t>
+          <t>Sehaj Bansal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vansh Bedi</t>
+          <t>Japneet Jain</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sneha Thind</t>
+          <t>Vihaan Gupta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Taranpreet Goyal</t>
+          <t>Jasleen Saini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Khushi Malhi</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aarav Gill</t>
+          <t>Uday Bedi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Rohan Sharma</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Sehaj Grewal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Japneet Bhatia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Vihaan Bansal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Jasleen Jain</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Pranav Gupta</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Tanvi Saini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Muskan Verma</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Noor Kapoor</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Hargun Pannu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Sukhmani Dhillon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Ishaan Rana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Nikita Mehta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Simran Aulakh</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Karan Kaur</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Mehakpreet Chawla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Gurnoor Gill</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Rajbir Sidhu</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Harleen Malhi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Navjot Sandhu</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Sanya Goyal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Gurleen Arora</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Jashan Thind</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Fatehbir Kaur</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Prabhleen Chawla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Diya Gill</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Meher Sidhu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Sahil Malhi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Aditi Sandhu</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Ekamjot Goyal</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Avneet Arora</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Manjot Thind</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Arjun Singh</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Manav Bedi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Riya Sharma</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Zoya Grewal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Arshdeep Bhatia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Yuvraj Bansal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Lovepreet Jain</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Ananya Gupta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Kavya Saini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Rahul Verma</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Vansh Kapoor</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Sneha Pannu</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Taranpreet Dhillon</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Khushi Rana</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Aarav Mehta</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Kabir Aulakh</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Rahul Gupta</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Vansh Saini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Sneha Verma</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Taranpreet Kapoor</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Khushi Pannu</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Aarav Dhillon</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Kabir Rana</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Priya Mehta</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Uday Aulakh</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Rohan Kaur</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Sehaj Chawla</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Japneet Gill</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Vihaan Sidhu</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Jasleen Malhi</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Pranav Sandhu</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Tanvi Goyal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Muskan Arora</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Noor Thind</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Hargun Singh</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Sukhmani Bedi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Ishaan Sharma</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Nikita Grewal</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Simran Bhatia</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Karan Bansal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Mehakpreet Jain</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Gurnoor Arora</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Rajbir Thind</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Harleen Singh</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Navjot Bedi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Sanya Sharma</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Gurleen Grewal</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Jashan Bhatia</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Fatehbir Bansal</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Prabhleen Jain</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Diya Gupta</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Meher Saini</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Sahil Verma</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Aditi Kapoor</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Ekamjot Pannu</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Avneet Dhillon</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Manjot Rana</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Arjun Mehta</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Manav Aulakh</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Riya Kaur</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Zoya Chawla</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Arshdeep Gill</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Yuvraj Sidhu</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Lovepreet Malhi</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Ananya Sandhu</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Kavya Goyal</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Riya Mehta</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Zoya Aulakh</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Yuvraj Chawla</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Lovepreet Gill</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Ananya Sidhu</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Kavya Malhi</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Rahul Sandhu</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Vansh Goyal</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Sneha Arora</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Taranpreet Thind</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Khushi Singh</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Aarav Bedi</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Kabir Sharma</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Priya Grewal</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Uday Bhatia</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Rohan Bansal</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Sehaj Jain</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Japneet Gupta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Vihaan Saini</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Jasleen Verma</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Pranav Kapoor</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Tanvi Pannu</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Muskan Dhillon</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Noor Rana</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Hargun Bansal</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Sukhmani Jain</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Ishaan Gupta</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Nikita Saini</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Simran Verma</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Karan Kapoor</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Mehakpreet Pannu</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Gurnoor Dhillon</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Rajbir Rana</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Harleen Mehta</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Navjot Aulakh</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Sanya Kaur</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Gurleen Chawla</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Jashan Gill</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Fatehbir Sidhu</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Prabhleen Malhi</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Diya Sandhu</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Meher Goyal</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Sahil Arora</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Aditi Thind</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Ekamjot Singh</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Avneet Bedi</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Manjot Sharma</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Arjun Grewal</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Manav Bhatia</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Sahil Sandhu</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Aditi Goyal</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Ekamjot Arora</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Avneet Thind</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Manjot Singh</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Arjun Bedi</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Manav Sharma</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Riya Grewal</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Zoya Bhatia</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Arshdeep Bansal</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Yuvraj Jain</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Lovepreet Gupta</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Ananya Saini</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Kavya Verma</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Rahul Kapoor</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Vansh Pannu</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Sneha Dhillon</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Taranpreet Rana</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Khushi Mehta</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Aarav Aulakh</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Kabir Kaur</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Priya Chawla</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Uday Gill</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Rohan Sidhu</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Sehaj Malhi</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Japneet Dhillon</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Vihaan Rana</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Jasleen Mehta</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Pranav Aulakh</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Tanvi Kaur</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Muskan Chawla</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Noor Gill</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Hargun Sidhu</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Sukhmani Malhi</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Ishaan Sandhu</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Nikita Goyal</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Simran Arora</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Karan Thind</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Mehakpreet Singh</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Gurnoor Bedi</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Rajbir Sharma</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Harleen Grewal</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Navjot Bhatia</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Sanya Bansal</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Gurleen Jain</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Jashan Gupta</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Fatehbir Saini</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Prabhleen Verma</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Diya Kapoor</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Meher Pannu</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Sanya Grewal</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Gurleen Bhatia</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Jashan Bansal</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Fatehbir Jain</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Prabhleen Gupta</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Diya Saini</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Meher Verma</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Sahil Kapoor</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Aditi Pannu</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Ekamjot Dhillon</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Avneet Rana</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Manjot Mehta</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Arjun Aulakh</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Manav Kaur</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Riya Chawla</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Zoya Gill</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Arshdeep Sidhu</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Yuvraj Malhi</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Lovepreet Sandhu</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Ananya Goyal</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Kavya Arora</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Rahul Thind</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Vansh Singh</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Sneha Bedi</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Taranpreet Sharma</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Khushi Sidhu</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Aarav Malhi</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Kabir Sandhu</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Priya Goyal</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Uday Arora</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Rohan Thind</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Sehaj Singh</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Japneet Bedi</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Vihaan Sharma</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Jasleen Grewal</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Pranav Bhatia</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Tanvi Bansal</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Muskan Jain</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Noor Gupta</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Hargun Saini</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Sukhmani Verma</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Ishaan Kapoor</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Nikita Pannu</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Simran Dhillon</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Karan Rana</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Mehakpreet Mehta</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Gurnoor Aulakh</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Rajbir Kaur</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Harleen Chawla</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Navjot Gill</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Simran Kapoor</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Karan Pannu</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Mehakpreet Dhillon</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Gurnoor Rana</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Rajbir Mehta</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Harleen Aulakh</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Navjot Kaur</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Sanya Chawla</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Gurleen Gill</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Jashan Sidhu</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -12609,7 +12609,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Fatehbir Malhi</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Prabhleen Sandhu</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Diya Goyal</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Meher Arora</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Sahil Thind</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Aditi Singh</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Ekamjot Bedi</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Avneet Sharma</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Manjot Grewal</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Arjun Bhatia</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Manav Bansal</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Riya Jain</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Zoya Gupta</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Arshdeep Saini</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Yuvraj Verma</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Lovepreet Bedi</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Ananya Sharma</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Kavya Grewal</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Rahul Bhatia</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Vansh Bansal</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Sneha Jain</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Taranpreet Gupta</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Khushi Saini</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Aarav Verma</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Kabir Kapoor</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Priya Pannu</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Uday Dhillon</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Rohan Rana</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Sehaj Mehta</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Japneet Aulakh</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Vihaan Kaur</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Jasleen Chawla</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Pranav Gill</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Tanvi Sidhu</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Muskan Malhi</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Noor Sandhu</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Hargun Goyal</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Sukhmani Arora</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Ishaan Thind</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Nikita Singh</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Tanvi Chawla</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Muskan Gill</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Noor Sidhu</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Hargun Malhi</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Sukhmani Sandhu</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Ishaan Goyal</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Nikita Arora</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Simran Thind</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Karan Singh</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Mehakpreet Bedi</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Gurnoor Sharma</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Rajbir Grewal</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Harleen Bhatia</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Navjot Bansal</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Sanya Jain</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Gurleen Gupta</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Jashan Saini</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Fatehbir Verma</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Prabhleen Kapoor</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Diya Pannu</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Meher Dhillon</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Sahil Rana</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Aditi Mehta</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Ekamjot Aulakh</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Avneet Kaur</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Manjot Saini</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Arjun Verma</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Manav Kapoor</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Riya Pannu</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Zoya Dhillon</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Arshdeep Rana</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Yuvraj Mehta</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Lovepreet Aulakh</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Ananya Kaur</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Kavya Chawla</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Rahul Gill</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Vansh Sidhu</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Sneha Malhi</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Taranpreet Sandhu</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Khushi Goyal</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Aarav Arora</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Kabir Thind</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Uday Bedi</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Rohan Sharma</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Sehaj Grewal</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Japneet Bhatia</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Vihaan Bansal</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Jasleen Jain</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Pranav Gupta</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Uday Thind</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Rohan Singh</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Sehaj Bedi</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Japneet Sharma</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Vihaan Grewal</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Jasleen Bhatia</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Pranav Bansal</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Tanvi Jain</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Muskan Gupta</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Noor Saini</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Hargun Verma</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Sukhmani Kapoor</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Nikita Dhillon</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Simran Rana</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Karan Mehta</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">

--- a/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -472,178 +472,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>then CSE, IT, ME and CE. Shared halls, the JPAL hour and the final-year CSE elective are set up by</t>
+          <t>then CSE, IT, ME and CE. Its file also has the lecture theatres, drawing halls and workshops of</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>the College Admin (they are already in the built-in GNDEC demo college).</t>
+          <t>first year. Not in the files: the JPAL hour and the final-year CSE elective (they need a student list</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>per group; they are in the built-in GNDEC demo college).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Timetabl.ai: one department's data</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Rows are checked before anything is saved; problems are shown row by row. A '*' marks a required column.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sections: one row per section (a group of students who always sit together).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab batches: how the section splits for labs, e.g. 'A1:30, A2:30' (name:students). Empty = whole section.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Teachers: one row per teacher of the department.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Name, Email (their login), Shifts (one or more shift names, comma separated), Max periods per day (default 5).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Subjects: one row per subject the department teaches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab equipment: what the lab room must have, e.g. computers. It must match a lab room's Equipment.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Can teach: which subjects each teacher can teach. Preference 1 = first choice, 2 = could also teach it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Used for teacher suggestions and to find a substitute when a teacher is on leave.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Classes: one row per class. Subject code, Sections (several separated by commas = one combined class),</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">  once that department's file is uploaded: upload Applied Sciences first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Rooms: rooms this department owns. Type: Lecture, Lab or Seminar. Seats. Equipment for labs.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shared halls (lecture theatres, seminar hall, drawing halls, workshops) are added by the College Admin in Setup.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rooms every department may use (e.g. a seminar hall) are added by the College Admin in Setup as shared rooms.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>rules and shared rooms. The College Admin sets those in Setup.</t>
         </is>

--- a/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_3_IT.xlsx
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2616001@gndec.demo</t>
+          <t>2616001@gndec.test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2616002@gndec.demo</t>
+          <t>2616002@gndec.test</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2616003@gndec.demo</t>
+          <t>2616003@gndec.test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2616004@gndec.demo</t>
+          <t>2616004@gndec.test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2616005@gndec.demo</t>
+          <t>2616005@gndec.test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2616006@gndec.demo</t>
+          <t>2616006@gndec.test</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2616007@gndec.demo</t>
+          <t>2616007@gndec.test</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2616008@gndec.demo</t>
+          <t>2616008@gndec.test</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2616009@gndec.demo</t>
+          <t>2616009@gndec.test</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2616010@gndec.demo</t>
+          <t>2616010@gndec.test</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2616011@gndec.demo</t>
+          <t>2616011@gndec.test</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2616012@gndec.demo</t>
+          <t>2616012@gndec.test</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2616013@gndec.demo</t>
+          <t>2616013@gndec.test</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2616014@gndec.demo</t>
+          <t>2616014@gndec.test</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2616015@gndec.demo</t>
+          <t>2616015@gndec.test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2616016@gndec.demo</t>
+          <t>2616016@gndec.test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2616017@gndec.demo</t>
+          <t>2616017@gndec.test</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2616018@gndec.demo</t>
+          <t>2616018@gndec.test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2616019@gndec.demo</t>
+          <t>2616019@gndec.test</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2616020@gndec.demo</t>
+          <t>2616020@gndec.test</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2616021@gndec.demo</t>
+          <t>2616021@gndec.test</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2616022@gndec.demo</t>
+          <t>2616022@gndec.test</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2616023@gndec.demo</t>
+          <t>2616023@gndec.test</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2616024@gndec.demo</t>
+          <t>2616024@gndec.test</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2616025@gndec.demo</t>
+          <t>2616025@gndec.test</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2616026@gndec.demo</t>
+          <t>2616026@gndec.test</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2616027@gndec.demo</t>
+          <t>2616027@gndec.test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2616028@gndec.demo</t>
+          <t>2616028@gndec.test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2616029@gndec.demo</t>
+          <t>2616029@gndec.test</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2616030@gndec.demo</t>
+          <t>2616030@gndec.test</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2616031@gndec.demo</t>
+          <t>2616031@gndec.test</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2616032@gndec.demo</t>
+          <t>2616032@gndec.test</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2616033@gndec.demo</t>
+          <t>2616033@gndec.test</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2616034@gndec.demo</t>
+          <t>2616034@gndec.test</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2616035@gndec.demo</t>
+          <t>2616035@gndec.test</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2616036@gndec.demo</t>
+          <t>2616036@gndec.test</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2616037@gndec.demo</t>
+          <t>2616037@gndec.test</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2616038@gndec.demo</t>
+          <t>2616038@gndec.test</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2616039@gndec.demo</t>
+          <t>2616039@gndec.test</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2616040@gndec.demo</t>
+          <t>2616040@gndec.test</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2616041@gndec.demo</t>
+          <t>2616041@gndec.test</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2616042@gndec.demo</t>
+          <t>2616042@gndec.test</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2616043@gndec.demo</t>
+          <t>2616043@gndec.test</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2616044@gndec.demo</t>
+          <t>2616044@gndec.test</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2616045@gndec.demo</t>
+          <t>2616045@gndec.test</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2616046@gndec.demo</t>
+          <t>2616046@gndec.test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2616047@gndec.demo</t>
+          <t>2616047@gndec.test</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2616048@gndec.demo</t>
+          <t>2616048@gndec.test</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2616049@gndec.demo</t>
+          <t>2616049@gndec.test</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2616050@gndec.demo</t>
+          <t>2616050@gndec.test</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2616051@gndec.demo</t>
+          <t>2616051@gndec.test</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2616052@gndec.demo</t>
+          <t>2616052@gndec.test</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2616053@gndec.demo</t>
+          <t>2616053@gndec.test</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2616054@gndec.demo</t>
+          <t>2616054@gndec.test</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2616055@gndec.demo</t>
+          <t>2616055@gndec.test</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2616056@gndec.demo</t>
+          <t>2616056@gndec.test</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2616057@gndec.demo</t>
+          <t>2616057@gndec.test</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2616058@gndec.demo</t>
+          <t>2616058@gndec.test</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2616059@gndec.demo</t>
+          <t>2616059@gndec.test</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2616060@gndec.demo</t>
+          <t>2616060@gndec.test</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2516001@gndec.demo</t>
+          <t>2516001@gndec.test</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2516002@gndec.demo</t>
+          <t>2516002@gndec.test</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2516003@gndec.demo</t>
+          <t>2516003@gndec.test</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2516004@gndec.demo</t>
+          <t>2516004@gndec.test</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2516005@gndec.demo</t>
+          <t>2516005@gndec.test</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2516006@gndec.demo</t>
+          <t>2516006@gndec.test</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2516007@gndec.demo</t>
+          <t>2516007@gndec.test</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2516008@gndec.demo</t>
+          <t>2516008@gndec.test</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2516009@gndec.demo</t>
+          <t>2516009@gndec.test</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2516010@gndec.demo</t>
+          <t>2516010@gndec.test</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2516011@gndec.demo</t>
+          <t>2516011@gndec.test</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2516012@gndec.demo</t>
+          <t>2516012@gndec.test</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2516013@gndec.demo</t>
+          <t>2516013@gndec.test</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2516014@gndec.demo</t>
+          <t>2516014@gndec.test</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2516015@gndec.demo</t>
+          <t>2516015@gndec.test</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2516016@gndec.demo</t>
+          <t>2516016@gndec.test</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2516017@gndec.demo</t>
+          <t>2516017@gndec.test</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2516018@gndec.demo</t>
+          <t>2516018@gndec.test</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2516019@gndec.demo</t>
+          <t>2516019@gndec.test</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2516020@gndec.demo</t>
+          <t>2516020@gndec.test</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2516021@gndec.demo</t>
+          <t>2516021@gndec.test</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2516022@gndec.demo</t>
+          <t>2516022@gndec.test</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2516023@gndec.demo</t>
+          <t>2516023@gndec.test</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2516024@gndec.demo</t>
+          <t>2516024@gndec.test</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2516025@gndec.demo</t>
+          <t>2516025@gndec.test</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2516026@gndec.demo</t>
+          <t>2516026@gndec.test</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2516027@gndec.demo</t>
+          <t>2516027@gndec.test</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2516028@gndec.demo</t>
+          <t>2516028@gndec.test</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2516029@gndec.demo</t>
+          <t>2516029@gndec.test</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2516030@gndec.demo</t>
+          <t>2516030@gndec.test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2516031@gndec.demo</t>
+          <t>2516031@gndec.test</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2516032@gndec.demo</t>
+          <t>2516032@gndec.test</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2516033@gndec.demo</t>
+          <t>2516033@gndec.test</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2516034@gndec.demo</t>
+          <t>2516034@gndec.test</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2516035@gndec.demo</t>
+          <t>2516035@gndec.test</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2516036@gndec.demo</t>
+          <t>2516036@gndec.test</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2516037@gndec.demo</t>
+          <t>2516037@gndec.test</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2516038@gndec.demo</t>
+          <t>2516038@gndec.test</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2516039@gndec.demo</t>
+          <t>2516039@gndec.test</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2516040@gndec.demo</t>
+          <t>2516040@gndec.test</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2516041@gndec.demo</t>
+          <t>2516041@gndec.test</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2516042@gndec.demo</t>
+          <t>2516042@gndec.test</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2516043@gndec.demo</t>
+          <t>2516043@gndec.test</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2516044@gndec.demo</t>
+          <t>2516044@gndec.test</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2516045@gndec.demo</t>
+          <t>2516045@gndec.test</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2516046@gndec.demo</t>
+          <t>2516046@gndec.test</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2516047@gndec.demo</t>
+          <t>2516047@gndec.test</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2516048@gndec.demo</t>
+          <t>2516048@gndec.test</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2516049@gndec.demo</t>
+          <t>2516049@gndec.test</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2516050@gndec.demo</t>
+          <t>2516050@gndec.test</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2516051@gndec.demo</t>
+          <t>2516051@gndec.test</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2516052@gndec.demo</t>
+          <t>2516052@gndec.test</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2516053@gndec.demo</t>
+          <t>2516053@gndec.test</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2516054@gndec.demo</t>
+          <t>2516054@gndec.test</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2516055@gndec.demo</t>
+          <t>2516055@gndec.test</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2516056@gndec.demo</t>
+          <t>2516056@gndec.test</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2516057@gndec.demo</t>
+          <t>2516057@gndec.test</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2516058@gndec.demo</t>
+          <t>2516058@gndec.test</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2516059@gndec.demo</t>
+          <t>2516059@gndec.test</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2516060@gndec.demo</t>
+          <t>2516060@gndec.test</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2516061@gndec.demo</t>
+          <t>2516061@gndec.test</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2516062@gndec.demo</t>
+          <t>2516062@gndec.test</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2516063@gndec.demo</t>
+          <t>2516063@gndec.test</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2516064@gndec.demo</t>
+          <t>2516064@gndec.test</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2516065@gndec.demo</t>
+          <t>2516065@gndec.test</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2516066@gndec.demo</t>
+          <t>2516066@gndec.test</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2516067@gndec.demo</t>
+          <t>2516067@gndec.test</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2516068@gndec.demo</t>
+          <t>2516068@gndec.test</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2516069@gndec.demo</t>
+          <t>2516069@gndec.test</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2516070@gndec.demo</t>
+          <t>2516070@gndec.test</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2516071@gndec.demo</t>
+          <t>2516071@gndec.test</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2516072@gndec.demo</t>
+          <t>2516072@gndec.test</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2516073@gndec.demo</t>
+          <t>2516073@gndec.test</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2516074@gndec.demo</t>
+          <t>2516074@gndec.test</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2516075@gndec.demo</t>
+          <t>2516075@gndec.test</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2516076@gndec.demo</t>
+          <t>2516076@gndec.test</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2516077@gndec.demo</t>
+          <t>2516077@gndec.test</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2516078@gndec.demo</t>
+          <t>2516078@gndec.test</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2516079@gndec.demo</t>
+          <t>2516079@gndec.test</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2516080@gndec.demo</t>
+          <t>2516080@gndec.test</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2516081@gndec.demo</t>
+          <t>2516081@gndec.test</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2516082@gndec.demo</t>
+          <t>2516082@gndec.test</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2516083@gndec.demo</t>
+          <t>2516083@gndec.test</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2516084@gndec.demo</t>
+          <t>2516084@gndec.test</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2516085@gndec.demo</t>
+          <t>2516085@gndec.test</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2516086@gndec.demo</t>
+          <t>2516086@gndec.test</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2516087@gndec.demo</t>
+          <t>2516087@gndec.test</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2516088@gndec.demo</t>
+          <t>2516088@gndec.test</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2516089@gndec.demo</t>
+          <t>2516089@gndec.test</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2516090@gndec.demo</t>
+          <t>2516090@gndec.test</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2516091@gndec.demo</t>
+          <t>2516091@gndec.test</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2516092@gndec.demo</t>
+          <t>2516092@gndec.test</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2516093@gndec.demo</t>
+          <t>2516093@gndec.test</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2516094@gndec.demo</t>
+          <t>2516094@gndec.test</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2516095@gndec.demo</t>
+          <t>2516095@gndec.test</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2516096@gndec.demo</t>
+          <t>2516096@gndec.test</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2516097@gndec.demo</t>
+          <t>2516097@gndec.test</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2516098@gndec.demo</t>
+          <t>2516098@gndec.test</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2516099@gndec.demo</t>
+          <t>2516099@gndec.test</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2516100@gndec.demo</t>
+          <t>2516100@gndec.test</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2516101@gndec.demo</t>
+          <t>2516101@gndec.test</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2516102@gndec.demo</t>
+          <t>2516102@gndec.test</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2516103@gndec.demo</t>
+          <t>2516103@gndec.test</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2516104@gndec.demo</t>
+          <t>2516104@gndec.test</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2516105@gndec.demo</t>
+          <t>2516105@gndec.test</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2516106@gndec.demo</t>
+          <t>2516106@gndec.test</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2516107@gndec.demo</t>
+          <t>2516107@gndec.test</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2516108@gndec.demo</t>
+          <t>2516108@gndec.test</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2516109@gndec.demo</t>
+          <t>2516109@gndec.test</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2516110@gndec.demo</t>
+          <t>2516110@gndec.test</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2516111@gndec.demo</t>
+          <t>2516111@gndec.test</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2516112@gndec.demo</t>
+          <t>2516112@gndec.test</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2516113@gndec.demo</t>
+          <t>2516113@gndec.test</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2516114@gndec.demo</t>
+          <t>2516114@gndec.test</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2516115@gndec.demo</t>
+          <t>2516115@gndec.test</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2516116@gndec.demo</t>
+          <t>2516116@gndec.test</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2516117@gndec.demo</t>
+          <t>2516117@gndec.test</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2516118@gndec.demo</t>
+          <t>2516118@gndec.test</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2416001@gndec.demo</t>
+          <t>2416001@gndec.test</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2416002@gndec.demo</t>
+          <t>2416002@gndec.test</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2416003@gndec.demo</t>
+          <t>2416003@gndec.test</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2416004@gndec.demo</t>
+          <t>2416004@gndec.test</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2416005@gndec.demo</t>
+          <t>2416005@gndec.test</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2416006@gndec.demo</t>
+          <t>2416006@gndec.test</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2416007@gndec.demo</t>
+          <t>2416007@gndec.test</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2416008@gndec.demo</t>
+          <t>2416008@gndec.test</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2416009@gndec.demo</t>
+          <t>2416009@gndec.test</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2416010@gndec.demo</t>
+          <t>2416010@gndec.test</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2416011@gndec.demo</t>
+          <t>2416011@gndec.test</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2416012@gndec.demo</t>
+          <t>2416012@gndec.test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2416013@gndec.demo</t>
+          <t>2416013@gndec.test</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2416014@gndec.demo</t>
+          <t>2416014@gndec.test</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2416015@gndec.demo</t>
+          <t>2416015@gndec.test</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2416016@gndec.demo</t>
+          <t>2416016@gndec.test</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2416017@gndec.demo</t>
+          <t>2416017@gndec.test</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2416018@gndec.demo</t>
+          <t>2416018@gndec.test</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2416019@gndec.demo</t>
+          <t>2416019@gndec.test</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2416020@gndec.demo</t>
+          <t>2416020@gndec.test</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2416021@gndec.demo</t>
+          <t>2416021@gndec.test</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2416022@gndec.demo</t>
+          <t>2416022@gndec.test</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2416023@gndec.demo</t>
+          <t>2416023@gndec.test</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2416024@gndec.demo</t>
+          <t>2416024@gndec.test</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2416025@gndec.demo</t>
+          <t>2416025@gndec.test</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2416026@gndec.demo</t>
+          <t>2416026@gndec.test</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2416027@gndec.demo</t>
+          <t>2416027@gndec.test</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2416028@gndec.demo</t>
+          <t>2416028@gndec.test</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2416029@gndec.demo</t>
+          <t>2416029@gndec.test</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2416030@gndec.demo</t>
+          <t>2416030@gndec.test</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2416031@gndec.demo</t>
+          <t>2416031@gndec.test</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2416032@gndec.demo</t>
+          <t>2416032@gndec.test</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2416033@gndec.demo</t>
+          <t>2416033@gndec.test</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2416034@gndec.demo</t>
+          <t>2416034@gndec.test</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2416035@gndec.demo</t>
+          <t>2416035@gndec.test</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2416036@gndec.demo</t>
+          <t>2416036@gndec.test</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2416037@gndec.demo</t>
+          <t>2416037@gndec.test</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2416038@gndec.demo</t>
+          <t>2416038@gndec.test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2416039@gndec.demo</t>
+          <t>2416039@gndec.test</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2416040@gndec.demo</t>
+          <t>2416040@gndec.test</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2416041@gndec.demo</t>
+          <t>2416041@gndec.test</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2416042@gndec.demo</t>
+          <t>2416042@gndec.test</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2416043@gndec.demo</t>
+          <t>2416043@gndec.test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2416044@gndec.demo</t>
+          <t>2416044@gndec.test</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2416045@gndec.demo</t>
+          <t>2416045@gndec.test</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2416046@gndec.demo</t>
+          <t>2416046@gndec.test</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2416047@gndec.demo</t>
+          <t>2416047@gndec.test</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2416048@gndec.demo</t>
+          <t>2416048@gndec.test</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2416049@gndec.demo</t>
+          <t>2416049@gndec.test</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2416050@gndec.demo</t>
+          <t>2416050@gndec.test</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2416051@gndec.demo</t>
+          <t>2416051@gndec.test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2416052@gndec.demo</t>
+          <t>2416052@gndec.test</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2416053@gndec.demo</t>
+          <t>2416053@gndec.test</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2416054@gndec.demo</t>
+          <t>2416054@gndec.test</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2416055@gndec.demo</t>
+          <t>2416055@gndec.test</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2416056@gndec.demo</t>
+          <t>2416056@gndec.test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2416057@gndec.demo</t>
+          <t>2416057@gndec.test</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2416058@gndec.demo</t>
+          <t>2416058@gndec.test</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2416059@gndec.demo</t>
+          <t>2416059@gndec.test</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2416060@gndec.demo</t>
+          <t>2416060@gndec.test</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2416061@gndec.demo</t>
+          <t>2416061@gndec.test</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2416062@gndec.demo</t>
+          <t>2416062@gndec.test</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2416063@gndec.demo</t>
+          <t>2416063@gndec.test</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2416064@gndec.demo</t>
+          <t>2416064@gndec.test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2416065@gndec.demo</t>
+          <t>2416065@gndec.test</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2416066@gndec.demo</t>
+          <t>2416066@gndec.test</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2416067@gndec.demo</t>
+          <t>2416067@gndec.test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2416068@gndec.demo</t>
+          <t>2416068@gndec.test</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2416069@gndec.demo</t>
+          <t>2416069@gndec.test</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2416070@gndec.demo</t>
+          <t>2416070@gndec.test</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2416071@gndec.demo</t>
+          <t>2416071@gndec.test</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2416072@gndec.demo</t>
+          <t>2416072@gndec.test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2416073@gndec.demo</t>
+          <t>2416073@gndec.test</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2416074@gndec.demo</t>
+          <t>2416074@gndec.test</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2416075@gndec.demo</t>
+          <t>2416075@gndec.test</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2416076@gndec.demo</t>
+          <t>2416076@gndec.test</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2416077@gndec.demo</t>
+          <t>2416077@gndec.test</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2416078@gndec.demo</t>
+          <t>2416078@gndec.test</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2416079@gndec.demo</t>
+          <t>2416079@gndec.test</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2416080@gndec.demo</t>
+          <t>2416080@gndec.test</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2416081@gndec.demo</t>
+          <t>2416081@gndec.test</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2416082@gndec.demo</t>
+          <t>2416082@gndec.test</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2416083@gndec.demo</t>
+          <t>2416083@gndec.test</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2416084@gndec.demo</t>
+          <t>2416084@gndec.test</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2416085@gndec.demo</t>
+          <t>2416085@gndec.test</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2416086@gndec.demo</t>
+          <t>2416086@gndec.test</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2416087@gndec.demo</t>
+          <t>2416087@gndec.test</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2416088@gndec.demo</t>
+          <t>2416088@gndec.test</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2416089@gndec.demo</t>
+          <t>2416089@gndec.test</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2416090@gndec.demo</t>
+          <t>2416090@gndec.test</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2416091@gndec.demo</t>
+          <t>2416091@gndec.test</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2416092@gndec.demo</t>
+          <t>2416092@gndec.test</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2416093@gndec.demo</t>
+          <t>2416093@gndec.test</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2416094@gndec.demo</t>
+          <t>2416094@gndec.test</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2416095@gndec.demo</t>
+          <t>2416095@gndec.test</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2416096@gndec.demo</t>
+          <t>2416096@gndec.test</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2416097@gndec.demo</t>
+          <t>2416097@gndec.test</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2416098@gndec.demo</t>
+          <t>2416098@gndec.test</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2416099@gndec.demo</t>
+          <t>2416099@gndec.test</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2416100@gndec.demo</t>
+          <t>2416100@gndec.test</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2416101@gndec.demo</t>
+          <t>2416101@gndec.test</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2416102@gndec.demo</t>
+          <t>2416102@gndec.test</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2416103@gndec.demo</t>
+          <t>2416103@gndec.test</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2416104@gndec.demo</t>
+          <t>2416104@gndec.test</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2416105@gndec.demo</t>
+          <t>2416105@gndec.test</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2416106@gndec.demo</t>
+          <t>2416106@gndec.test</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2416107@gndec.demo</t>
+          <t>2416107@gndec.test</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2416108@gndec.demo</t>
+          <t>2416108@gndec.test</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2416109@gndec.demo</t>
+          <t>2416109@gndec.test</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2416110@gndec.demo</t>
+          <t>2416110@gndec.test</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2416111@gndec.demo</t>
+          <t>2416111@gndec.test</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2416112@gndec.demo</t>
+          <t>2416112@gndec.test</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2416113@gndec.demo</t>
+          <t>2416113@gndec.test</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2416114@gndec.demo</t>
+          <t>2416114@gndec.test</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2416115@gndec.demo</t>
+          <t>2416115@gndec.test</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2416116@gndec.demo</t>
+          <t>2416116@gndec.test</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2416117@gndec.demo</t>
+          <t>2416117@gndec.test</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2416118@gndec.demo</t>
+          <t>2416118@gndec.test</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2316001@gndec.demo</t>
+          <t>2316001@gndec.test</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2316002@gndec.demo</t>
+          <t>2316002@gndec.test</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2316003@gndec.demo</t>
+          <t>2316003@gndec.test</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2316004@gndec.demo</t>
+          <t>2316004@gndec.test</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2316005@gndec.demo</t>
+          <t>2316005@gndec.test</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2316006@gndec.demo</t>
+          <t>2316006@gndec.test</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2316007@gndec.demo</t>
+          <t>2316007@gndec.test</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2316008@gndec.demo</t>
+          <t>2316008@gndec.test</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2316009@gndec.demo</t>
+          <t>2316009@gndec.test</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2316010@gndec.demo</t>
+          <t>2316010@gndec.test</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2316011@gndec.demo</t>
+          <t>2316011@gndec.test</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2316012@gndec.demo</t>
+          <t>2316012@gndec.test</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2316013@gndec.demo</t>
+          <t>2316013@gndec.test</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2316014@gndec.demo</t>
+          <t>2316014@gndec.test</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2316015@gndec.demo</t>
+          <t>2316015@gndec.test</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2316016@gndec.demo</t>
+          <t>2316016@gndec.test</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2316017@gndec.demo</t>
+          <t>2316017@gndec.test</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2316018@gndec.demo</t>
+          <t>2316018@gndec.test</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2316019@gndec.demo</t>
+          <t>2316019@gndec.test</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2316020@gndec.demo</t>
+          <t>2316020@gndec.test</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2316021@gndec.demo</t>
+          <t>2316021@gndec.test</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2316022@gndec.demo</t>
+          <t>2316022@gndec.test</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2316023@gndec.demo</t>
+          <t>2316023@gndec.test</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2316024@gndec.demo</t>
+          <t>2316024@gndec.test</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2316025@gndec.demo</t>
+          <t>2316025@gndec.test</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2316026@gndec.demo</t>
+          <t>2316026@gndec.test</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2316027@gndec.demo</t>
+          <t>2316027@gndec.test</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2316028@gndec.demo</t>
+          <t>2316028@gndec.test</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2316029@gndec.demo</t>
+          <t>2316029@gndec.test</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2316030@gndec.demo</t>
+          <t>2316030@gndec.test</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2316031@gndec.demo</t>
+          <t>2316031@gndec.test</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2316032@gndec.demo</t>
+          <t>2316032@gndec.test</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2316033@gndec.demo</t>
+          <t>2316033@gndec.test</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2316034@gndec.demo</t>
+          <t>2316034@gndec.test</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2316035@gndec.demo</t>
+          <t>2316035@gndec.test</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2316036@gndec.demo</t>
+          <t>2316036@gndec.test</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2316037@gndec.demo</t>
+          <t>2316037@gndec.test</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2316038@gndec.demo</t>
+          <t>2316038@gndec.test</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2316039@gndec.demo</t>
+          <t>2316039@gndec.test</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2316040@gndec.demo</t>
+          <t>2316040@gndec.test</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2316041@gndec.demo</t>
+          <t>2316041@gndec.test</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2316042@gndec.demo</t>
+          <t>2316042@gndec.test</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2316043@gndec.demo</t>
+          <t>2316043@gndec.test</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2316044@gndec.demo</t>
+          <t>2316044@gndec.test</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2316045@gndec.demo</t>
+          <t>2316045@gndec.test</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2316046@gndec.demo</t>
+          <t>2316046@gndec.test</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2316047@gndec.demo</t>
+          <t>2316047@gndec.test</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2316048@gndec.demo</t>
+          <t>2316048@gndec.test</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2316049@gndec.demo</t>
+          <t>2316049@gndec.test</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2316050@gndec.demo</t>
+          <t>2316050@gndec.test</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2316051@gndec.demo</t>
+          <t>2316051@gndec.test</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2316052@gndec.demo</t>
+          <t>2316052@gndec.test</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2316053@gndec.demo</t>
+          <t>2316053@gndec.test</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2316054@gndec.demo</t>
+          <t>2316054@gndec.test</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2316055@gndec.demo</t>
+          <t>2316055@gndec.test</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2316056@gndec.demo</t>
+          <t>2316056@gndec.test</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2316057@gndec.demo</t>
+          <t>2316057@gndec.test</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2316058@gndec.demo</t>
+          <t>2316058@gndec.test</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2316059@gndec.demo</t>
+          <t>2316059@gndec.test</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2316060@gndec.demo</t>
+          <t>2316060@gndec.test</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2316061@gndec.demo</t>
+          <t>2316061@gndec.test</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2316062@gndec.demo</t>
+          <t>2316062@gndec.test</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2316063@gndec.demo</t>
+          <t>2316063@gndec.test</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2316064@gndec.demo</t>
+          <t>2316064@gndec.test</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2316065@gndec.demo</t>
+          <t>2316065@gndec.test</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2316066@gndec.demo</t>
+          <t>2316066@gndec.test</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2316067@gndec.demo</t>
+          <t>2316067@gndec.test</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2316068@gndec.demo</t>
+          <t>2316068@gndec.test</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2316069@gndec.demo</t>
+          <t>2316069@gndec.test</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2316070@gndec.demo</t>
+          <t>2316070@gndec.test</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2316071@gndec.demo</t>
+          <t>2316071@gndec.test</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2316072@gndec.demo</t>
+          <t>2316072@gndec.test</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2316073@gndec.demo</t>
+          <t>2316073@gndec.test</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2316074@gndec.demo</t>
+          <t>2316074@gndec.test</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2316075@gndec.demo</t>
+          <t>2316075@gndec.test</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2316076@gndec.demo</t>
+          <t>2316076@gndec.test</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2316077@gndec.demo</t>
+          <t>2316077@gndec.test</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2316078@gndec.demo</t>
+          <t>2316078@gndec.test</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2316079@gndec.demo</t>
+          <t>2316079@gndec.test</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2316080@gndec.demo</t>
+          <t>2316080@gndec.test</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2316081@gndec.demo</t>
+          <t>2316081@gndec.test</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2316082@gndec.demo</t>
+          <t>2316082@gndec.test</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2316083@gndec.demo</t>
+          <t>2316083@gndec.test</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2316084@gndec.demo</t>
+          <t>2316084@gndec.test</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2316085@gndec.demo</t>
+          <t>2316085@gndec.test</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2316086@gndec.demo</t>
+          <t>2316086@gndec.test</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2316087@gndec.demo</t>
+          <t>2316087@gndec.test</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2316088@gndec.demo</t>
+          <t>2316088@gndec.test</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2316089@gndec.demo</t>
+          <t>2316089@gndec.test</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2316090@gndec.demo</t>
+          <t>2316090@gndec.test</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2316091@gndec.demo</t>
+          <t>2316091@gndec.test</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2316092@gndec.demo</t>
+          <t>2316092@gndec.test</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2316093@gndec.demo</t>
+          <t>2316093@gndec.test</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2316094@gndec.demo</t>
+          <t>2316094@gndec.test</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2316095@gndec.demo</t>
+          <t>2316095@gndec.test</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2316096@gndec.demo</t>
+          <t>2316096@gndec.test</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2316097@gndec.demo</t>
+          <t>2316097@gndec.test</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2316098@gndec.demo</t>
+          <t>2316098@gndec.test</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2316099@gndec.demo</t>
+          <t>2316099@gndec.test</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2316100@gndec.demo</t>
+          <t>2316100@gndec.test</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2316101@gndec.demo</t>
+          <t>2316101@gndec.test</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2316102@gndec.demo</t>
+          <t>2316102@gndec.test</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2316103@gndec.demo</t>
+          <t>2316103@gndec.test</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2316104@gndec.demo</t>
+          <t>2316104@gndec.test</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2316105@gndec.demo</t>
+          <t>2316105@gndec.test</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2316106@gndec.demo</t>
+          <t>2316106@gndec.test</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2316107@gndec.demo</t>
+          <t>2316107@gndec.test</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2316108@gndec.demo</t>
+          <t>2316108@gndec.test</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2316109@gndec.demo</t>
+          <t>2316109@gndec.test</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2316110@gndec.demo</t>
+          <t>2316110@gndec.test</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2316111@gndec.demo</t>
+          <t>2316111@gndec.test</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2316112@gndec.demo</t>
+          <t>2316112@gndec.test</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2316113@gndec.demo</t>
+          <t>2316113@gndec.test</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2316114@gndec.demo</t>
+          <t>2316114@gndec.test</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2316115@gndec.demo</t>
+          <t>2316115@gndec.test</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2316116@gndec.demo</t>
+          <t>2316116@gndec.test</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2316117@gndec.demo</t>
+          <t>2316117@gndec.test</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2316118@gndec.demo</t>
+          <t>2316118@gndec.test</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
